--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_magallanes_y_la_antartica_chilena.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.04699738903394</v>
+      </c>
+      <c r="C2">
         <v>28.724123461395</v>
-      </c>
-      <c r="C2">
-        <v>29.04699738903394</v>
       </c>
       <c r="D2">
         <v>3.481394310757619</v>
       </c>
       <c r="E2">
-        <v>18.20619851501607</v>
+        <v>18.41084555428318</v>
       </c>
       <c r="F2">
         <v>63.38295593070075</v>
       </c>
       <c r="G2">
-        <v>18.41084555428318</v>
+        <v>18.20619851501607</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>33.64485981308411</v>
+      </c>
+      <c r="C3">
         <v>32.71028037383177</v>
-      </c>
-      <c r="C3">
-        <v>33.64485981308411</v>
       </c>
       <c r="D3">
         <v>3.057142857142857</v>
       </c>
       <c r="E3">
-        <v>19.6629213483146</v>
+        <v>20.2247191011236</v>
       </c>
       <c r="F3">
         <v>60.1123595505618</v>
       </c>
       <c r="G3">
-        <v>20.2247191011236</v>
+        <v>19.6629213483146</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>15.84158415841584</v>
+      </c>
+      <c r="C4">
         <v>31.68316831683168</v>
-      </c>
-      <c r="C4">
-        <v>15.84158415841584</v>
       </c>
       <c r="D4">
         <v>3.15625</v>
       </c>
       <c r="E4">
-        <v>21.47651006711409</v>
+        <v>10.73825503355705</v>
       </c>
       <c r="F4">
         <v>67.78523489932887</v>
       </c>
       <c r="G4">
-        <v>10.73825503355705</v>
+        <v>21.47651006711409</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>37.03703703703704</v>
+      </c>
+      <c r="C5">
         <v>30.24691358024691</v>
-      </c>
-      <c r="C5">
-        <v>37.03703703703704</v>
       </c>
       <c r="D5">
         <v>3.306122448979592</v>
       </c>
       <c r="E5">
-        <v>18.08118081180812</v>
+        <v>22.14022140221402</v>
       </c>
       <c r="F5">
         <v>59.77859778597786</v>
       </c>
       <c r="G5">
-        <v>22.14022140221402</v>
+        <v>18.08118081180812</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>45.09803921568628</v>
+      </c>
+      <c r="C6">
         <v>10.40723981900453</v>
-      </c>
-      <c r="C6">
-        <v>45.09803921568628</v>
       </c>
       <c r="D6">
         <v>9.608695652173912</v>
       </c>
       <c r="E6">
-        <v>6.692531522793405</v>
+        <v>29.00096993210475</v>
       </c>
       <c r="F6">
         <v>64.30649854510185</v>
       </c>
       <c r="G6">
-        <v>29.00096993210475</v>
+        <v>6.692531522793405</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>31.35514018691589</v>
+      </c>
+      <c r="C7">
         <v>24.92990654205607</v>
-      </c>
-      <c r="C7">
-        <v>31.35514018691589</v>
       </c>
       <c r="D7">
         <v>4.01124648547329</v>
       </c>
       <c r="E7">
-        <v>15.95156226640753</v>
+        <v>20.0627896546569</v>
       </c>
       <c r="F7">
         <v>63.98564807893557</v>
       </c>
       <c r="G7">
-        <v>20.0627896546569</v>
+        <v>15.95156226640753</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>41.27358490566038</v>
+      </c>
+      <c r="C8">
         <v>27.83018867924528</v>
-      </c>
-      <c r="C8">
-        <v>41.27358490566038</v>
       </c>
       <c r="D8">
         <v>3.593220338983051</v>
       </c>
       <c r="E8">
-        <v>16.45746164574616</v>
+        <v>24.40725244072524</v>
       </c>
       <c r="F8">
         <v>59.13528591352859</v>
       </c>
       <c r="G8">
-        <v>24.40725244072524</v>
+        <v>16.45746164574616</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>21.95121951219512</v>
+      </c>
+      <c r="C9">
         <v>25.60975609756098</v>
-      </c>
-      <c r="C9">
-        <v>21.95121951219512</v>
       </c>
       <c r="D9">
         <v>3.904761904761905</v>
       </c>
       <c r="E9">
-        <v>17.35537190082645</v>
+        <v>14.87603305785124</v>
       </c>
       <c r="F9">
         <v>67.76859504132231</v>
       </c>
       <c r="G9">
-        <v>14.87603305785124</v>
+        <v>17.35537190082645</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.42561088772038</v>
+      </c>
+      <c r="C10">
         <v>29.26074853077637</v>
-      </c>
-      <c r="C10">
-        <v>28.42561088772038</v>
       </c>
       <c r="D10">
         <v>3.41754756871036</v>
       </c>
       <c r="E10">
-        <v>18.55629658689682</v>
+        <v>18.0266771282856</v>
       </c>
       <c r="F10">
         <v>63.41702628481757</v>
       </c>
       <c r="G10">
-        <v>18.0266771282856</v>
+        <v>18.55629658689682</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>19.23076923076923</v>
+      </c>
+      <c r="C11">
         <v>17.30769230769231</v>
-      </c>
-      <c r="C11">
-        <v>19.23076923076923</v>
       </c>
       <c r="D11">
         <v>5.777777777777778</v>
       </c>
       <c r="E11">
-        <v>12.67605633802817</v>
+        <v>14.08450704225352</v>
       </c>
       <c r="F11">
         <v>73.2394366197183</v>
       </c>
       <c r="G11">
-        <v>14.08450704225352</v>
+        <v>12.67605633802817</v>
       </c>
     </row>
   </sheetData>
